--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/4.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/4.xlsx
@@ -426,13 +426,13 @@
         <v>-8.265928534185642</v>
       </c>
       <c r="E2">
-        <v>-5.912074333363507</v>
+        <v>-2.837557475335871</v>
       </c>
       <c r="F2">
-        <v>-4.13600628309673</v>
+        <v>-3.902588916335886</v>
       </c>
       <c r="G2">
-        <v>-10.17620763074109</v>
+        <v>-10.07922519916814</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.878680607262648</v>
       </c>
       <c r="E3">
-        <v>-5.537605760721229</v>
+        <v>-3.151978482636439</v>
       </c>
       <c r="F3">
-        <v>-4.482729399947297</v>
+        <v>-3.650006441343872</v>
       </c>
       <c r="G3">
-        <v>-10.82671658702573</v>
+        <v>-9.795458477723974</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.652181751104427</v>
       </c>
       <c r="E4">
-        <v>-5.640402120695347</v>
+        <v>-3.52694518741956</v>
       </c>
       <c r="F4">
-        <v>-4.061148377640545</v>
+        <v>-3.91500614370385</v>
       </c>
       <c r="G4">
-        <v>-8.781047734671576</v>
+        <v>-9.778587937655848</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.46677976478389</v>
       </c>
       <c r="E5">
-        <v>-5.875112928512901</v>
+        <v>-4.560152760061613</v>
       </c>
       <c r="F5">
-        <v>-3.887304709386832</v>
+        <v>-3.476163601457562</v>
       </c>
       <c r="G5">
-        <v>-9.792591545286966</v>
+        <v>-9.559433133501635</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.29226956204858</v>
       </c>
       <c r="E6">
-        <v>-7.363785359898424</v>
+        <v>-5.312762497766388</v>
       </c>
       <c r="F6">
-        <v>-3.957841022102612</v>
+        <v>-3.197702100434688</v>
       </c>
       <c r="G6">
-        <v>-9.876884655807888</v>
+        <v>-9.663645796532354</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.05807410869544</v>
       </c>
       <c r="E7">
-        <v>-8.194072012256768</v>
+        <v>-7.029774174040674</v>
       </c>
       <c r="F7">
-        <v>-4.005129203658825</v>
+        <v>-3.321866918807709</v>
       </c>
       <c r="G7">
-        <v>-9.864996486776366</v>
+        <v>-9.651655000589113</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.70793514593088</v>
       </c>
       <c r="E8">
-        <v>-10.21875726956019</v>
+        <v>-6.895663416303516</v>
       </c>
       <c r="F8">
-        <v>-3.642252922453668</v>
+        <v>-3.465958943422474</v>
       </c>
       <c r="G8">
-        <v>-10.63719447599353</v>
+        <v>-9.201589645070735</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.1654406997896</v>
       </c>
       <c r="E9">
-        <v>-10.00174826663862</v>
+        <v>-7.953116438782637</v>
       </c>
       <c r="F9">
-        <v>-3.722836503398004</v>
+        <v>-3.095651378246803</v>
       </c>
       <c r="G9">
-        <v>-9.74833286197245</v>
+        <v>-8.78707292755305</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.36628007420705</v>
       </c>
       <c r="E10">
-        <v>-10.79252398328004</v>
+        <v>-8.113152710213708</v>
       </c>
       <c r="F10">
-        <v>-3.572821651853222</v>
+        <v>-3.16016794504644</v>
       </c>
       <c r="G10">
-        <v>-9.05993140144532</v>
+        <v>-9.042120666444042</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.25465060359821</v>
       </c>
       <c r="E11">
-        <v>-10.57938229716102</v>
+        <v>-9.644039576298733</v>
       </c>
       <c r="F11">
-        <v>-3.35593104314563</v>
+        <v>-2.568419549019599</v>
       </c>
       <c r="G11">
-        <v>-9.052462810708725</v>
+        <v>-8.836635104821479</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.79706060360348</v>
       </c>
       <c r="E12">
-        <v>-10.68461950462527</v>
+        <v>-9.978657577673511</v>
       </c>
       <c r="F12">
-        <v>-3.295715359901328</v>
+        <v>-2.673610612031497</v>
       </c>
       <c r="G12">
-        <v>-8.269191046662701</v>
+        <v>-8.249294667971681</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.97906837599346</v>
       </c>
       <c r="E13">
-        <v>-12.27166397687942</v>
+        <v>-10.17008975939976</v>
       </c>
       <c r="F13">
-        <v>-2.933399055060464</v>
+        <v>-2.268727819830377</v>
       </c>
       <c r="G13">
-        <v>-9.173138816706238</v>
+        <v>-8.31834271628426</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.8242499076515</v>
       </c>
       <c r="E14">
-        <v>-13.26349035403938</v>
+        <v>-10.91091187926257</v>
       </c>
       <c r="F14">
-        <v>-2.686533143515169</v>
+        <v>-2.486828673313459</v>
       </c>
       <c r="G14">
-        <v>-7.832222209297679</v>
+        <v>-7.64697732310222</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.383790221506628</v>
       </c>
       <c r="E15">
-        <v>-13.12990942776112</v>
+        <v>-12.02270658983373</v>
       </c>
       <c r="F15">
-        <v>-2.902632661353088</v>
+        <v>-2.248874338287481</v>
       </c>
       <c r="G15">
-        <v>-8.641369197278646</v>
+        <v>-7.311681960339295</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.731184357768473</v>
       </c>
       <c r="E16">
-        <v>-14.15585785656888</v>
+        <v>-12.57708237785274</v>
       </c>
       <c r="F16">
-        <v>-2.293550677422667</v>
+        <v>-1.748740891908057</v>
       </c>
       <c r="G16">
-        <v>-8.387407317324536</v>
+        <v>-6.723139795458742</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.956721243864282</v>
       </c>
       <c r="E17">
-        <v>-14.67190464058696</v>
+        <v>-13.24863695929422</v>
       </c>
       <c r="F17">
-        <v>-2.115404468878814</v>
+        <v>-1.712410354356076</v>
       </c>
       <c r="G17">
-        <v>-6.984666271970087</v>
+        <v>-6.361267373106548</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.164739288641677</v>
       </c>
       <c r="E18">
-        <v>-15.56337550526294</v>
+        <v>-14.74223637040009</v>
       </c>
       <c r="F18">
-        <v>-2.002516215960103</v>
+        <v>-1.216664770109282</v>
       </c>
       <c r="G18">
-        <v>-7.027822543620027</v>
+        <v>-5.529016087807007</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.458126046998417</v>
       </c>
       <c r="E19">
-        <v>-17.57089784607729</v>
+        <v>-14.92091184084673</v>
       </c>
       <c r="F19">
-        <v>-1.484803156558468</v>
+        <v>-1.124577651042269</v>
       </c>
       <c r="G19">
-        <v>-5.782544286295473</v>
+        <v>-5.884115133985853</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.9277314543650752</v>
       </c>
       <c r="E20">
-        <v>-16.57818841648584</v>
+        <v>-15.58640279559194</v>
       </c>
       <c r="F20">
-        <v>-1.451646094526612</v>
+        <v>-0.9320708652034835</v>
       </c>
       <c r="G20">
-        <v>-6.198514333304898</v>
+        <v>-5.675484554100983</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.3468124915745441</v>
       </c>
       <c r="E21">
-        <v>-18.91111784254337</v>
+        <v>-16.00184047258162</v>
       </c>
       <c r="F21">
-        <v>-1.18396165341416</v>
+        <v>-0.8332756269086005</v>
       </c>
       <c r="G21">
-        <v>-6.399467758084199</v>
+        <v>-5.039323502183553</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.311176439527289</v>
       </c>
       <c r="E22">
-        <v>-18.73019624898892</v>
+        <v>-16.33961482033974</v>
       </c>
       <c r="F22">
-        <v>-1.079459792081391</v>
+        <v>-0.3723446678666631</v>
       </c>
       <c r="G22">
-        <v>-5.791651597074009</v>
+        <v>-4.972817952845134</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.938468235283145</v>
       </c>
       <c r="E23">
-        <v>-19.09173149986529</v>
+        <v>-16.99942706867933</v>
       </c>
       <c r="F23">
-        <v>-0.7918688539122644</v>
+        <v>-0.2083121831317078</v>
       </c>
       <c r="G23">
-        <v>-5.031123280882777</v>
+        <v>-4.817066716859042</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.230119364384097</v>
       </c>
       <c r="E24">
-        <v>-19.08987029704814</v>
+        <v>-18.33494650912544</v>
       </c>
       <c r="F24">
-        <v>-0.7502384217171724</v>
+        <v>0.06049718091374574</v>
       </c>
       <c r="G24">
-        <v>-6.120418564033491</v>
+        <v>-4.413358930527078</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.202060145082642</v>
       </c>
       <c r="E25">
-        <v>-19.29336180505681</v>
+        <v>-18.08574458448334</v>
       </c>
       <c r="F25">
-        <v>-0.1335354576809964</v>
+        <v>0.04472755066665155</v>
       </c>
       <c r="G25">
-        <v>-5.563541767236067</v>
+        <v>-4.67740142164827</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.886228244438684</v>
       </c>
       <c r="E26">
-        <v>-20.35359983905065</v>
+        <v>-18.23248072775389</v>
       </c>
       <c r="F26">
-        <v>0.1625752392259232</v>
+        <v>0.2356538115008956</v>
       </c>
       <c r="G26">
-        <v>-5.171122941193017</v>
+        <v>-5.256952144844162</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.325196507864765</v>
       </c>
       <c r="E27">
-        <v>-19.98821085679375</v>
+        <v>-18.76737049211789</v>
       </c>
       <c r="F27">
-        <v>-0.267273718128171</v>
+        <v>0.2870796882340917</v>
       </c>
       <c r="G27">
-        <v>-5.936209878591824</v>
+        <v>-4.631030610279698</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.566685438730517</v>
       </c>
       <c r="E28">
-        <v>-20.86079798485775</v>
+        <v>-19.04915931571918</v>
       </c>
       <c r="F28">
-        <v>-0.2914579044529026</v>
+        <v>0.3041672510190399</v>
       </c>
       <c r="G28">
-        <v>-6.246288815982121</v>
+        <v>-5.370768700484305</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.337391220071765</v>
       </c>
       <c r="E29">
-        <v>-20.21190841582466</v>
+        <v>-17.92893711501974</v>
       </c>
       <c r="F29">
-        <v>-0.2671188134238475</v>
+        <v>0.288590630376798</v>
       </c>
       <c r="G29">
-        <v>-5.515280634364571</v>
+        <v>-5.340914200811158</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.338240362571906</v>
       </c>
       <c r="E30">
-        <v>-20.78255501095322</v>
+        <v>-18.27323246534891</v>
       </c>
       <c r="F30">
-        <v>-0.2977071081396221</v>
+        <v>0.3756421040021924</v>
       </c>
       <c r="G30">
-        <v>-6.540811499883382</v>
+        <v>-5.944115461339604</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.384310173551066</v>
       </c>
       <c r="E31">
-        <v>-19.53650915995066</v>
+        <v>-18.15422869690135</v>
       </c>
       <c r="F31">
-        <v>-0.2203806678230938</v>
+        <v>0.09953979334249204</v>
       </c>
       <c r="G31">
-        <v>-6.931839896799938</v>
+        <v>-4.794641081376019</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.426336053126203</v>
       </c>
       <c r="E32">
-        <v>-19.85839762088987</v>
+        <v>-18.17848320368643</v>
       </c>
       <c r="F32">
-        <v>-0.6502213415031601</v>
+        <v>0.02061046210154675</v>
       </c>
       <c r="G32">
-        <v>-6.4374364048741</v>
+        <v>-5.140030297488182</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.419978211535933</v>
       </c>
       <c r="E33">
-        <v>-19.67531594523377</v>
+        <v>-17.78969106775789</v>
       </c>
       <c r="F33">
-        <v>-0.1439952528761458</v>
+        <v>0.1534234361597943</v>
       </c>
       <c r="G33">
-        <v>-5.823174611698949</v>
+        <v>-5.491130204655588</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.328040623879355</v>
       </c>
       <c r="E34">
-        <v>-19.39197838352185</v>
+        <v>-17.49434852145163</v>
       </c>
       <c r="F34">
-        <v>-0.8034585422448323</v>
+        <v>-0.0860385275392784</v>
       </c>
       <c r="G34">
-        <v>-6.62144645758341</v>
+        <v>-4.54798557542708</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.117224836866389</v>
       </c>
       <c r="E35">
-        <v>-19.5811644421403</v>
+        <v>-17.47943625654437</v>
       </c>
       <c r="F35">
-        <v>-0.5461518879546526</v>
+        <v>0.08165948295306472</v>
       </c>
       <c r="G35">
-        <v>-5.786503698760442</v>
+        <v>-5.795683841540841</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.757309887691082</v>
       </c>
       <c r="E36">
-        <v>-17.59627994289029</v>
+        <v>-16.73219276053869</v>
       </c>
       <c r="F36">
-        <v>-0.5439790802571095</v>
+        <v>-0.2456723813653683</v>
       </c>
       <c r="G36">
-        <v>-5.773572707884049</v>
+        <v>-5.306441490110727</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.225182641436162</v>
       </c>
       <c r="E37">
-        <v>-18.69867354142153</v>
+        <v>-16.25241452484804</v>
       </c>
       <c r="F37">
-        <v>-1.045842157773579</v>
+        <v>0.01928258915485914</v>
       </c>
       <c r="G37">
-        <v>-5.994250362986326</v>
+        <v>-4.851698333745358</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.502324159220543</v>
       </c>
       <c r="E38">
-        <v>-17.56577614197462</v>
+        <v>-16.01461076928324</v>
       </c>
       <c r="F38">
-        <v>-1.024861268195473</v>
+        <v>-0.4150900825859232</v>
       </c>
       <c r="G38">
-        <v>-4.990145348197679</v>
+        <v>-5.165101058857083</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.57633425457484</v>
       </c>
       <c r="E39">
-        <v>-18.11987569307916</v>
+        <v>-15.42439210949353</v>
       </c>
       <c r="F39">
-        <v>-0.3453755103337196</v>
+        <v>-0.285328814039589</v>
       </c>
       <c r="G39">
-        <v>-5.568779050279193</v>
+        <v>-4.091093875006725</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.445003821374462</v>
       </c>
       <c r="E40">
-        <v>-17.35715387291526</v>
+        <v>-15.20719743913764</v>
       </c>
       <c r="F40">
-        <v>-0.756470229688433</v>
+        <v>-0.4452004093102824</v>
       </c>
       <c r="G40">
-        <v>-4.462735717245308</v>
+        <v>-4.626217077065598</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.117368698583157</v>
       </c>
       <c r="E41">
-        <v>-17.62111409434835</v>
+        <v>-14.79420060963811</v>
       </c>
       <c r="F41">
-        <v>-0.7892768923089047</v>
+        <v>-0.3225249955274953</v>
       </c>
       <c r="G41">
-        <v>-4.650652213690958</v>
+        <v>-3.96874273296634</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.61073507655988</v>
       </c>
       <c r="E42">
-        <v>-16.91259810805626</v>
+        <v>-13.43864267170805</v>
       </c>
       <c r="F42">
-        <v>-0.9969800781520471</v>
+        <v>-0.2456897770808271</v>
       </c>
       <c r="G42">
-        <v>-4.892904694072667</v>
+        <v>-4.250748244183616</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.95306792888701</v>
       </c>
       <c r="E43">
-        <v>-14.99427311977099</v>
+        <v>-13.95158745103088</v>
       </c>
       <c r="F43">
-        <v>-0.3918941385727315</v>
+        <v>-0.7989464250017834</v>
       </c>
       <c r="G43">
-        <v>-4.861881571824156</v>
+        <v>-3.802867848721157</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.181275517651889</v>
       </c>
       <c r="E44">
-        <v>-15.05237796976341</v>
+        <v>-12.83013803387537</v>
       </c>
       <c r="F44">
-        <v>-1.210534022961163</v>
+        <v>-0.7172263239808065</v>
       </c>
       <c r="G44">
-        <v>-4.015994149448358</v>
+        <v>-3.999841997762253</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.33909888424151</v>
       </c>
       <c r="E45">
-        <v>-15.20125155276557</v>
+        <v>-12.77190638661073</v>
       </c>
       <c r="F45">
-        <v>-1.178384255691111</v>
+        <v>-0.5551388459076244</v>
       </c>
       <c r="G45">
-        <v>-4.686376310605233</v>
+        <v>-3.679000476823786</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.476468765529572</v>
       </c>
       <c r="E46">
-        <v>-14.20915799563916</v>
+        <v>-12.48362373128244</v>
       </c>
       <c r="F46">
-        <v>-1.665799777335354</v>
+        <v>-1.046694547831059</v>
       </c>
       <c r="G46">
-        <v>-4.372235333838251</v>
+        <v>-2.930502683122267</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.647543354830831</v>
       </c>
       <c r="E47">
-        <v>-14.6010204369449</v>
+        <v>-12.37224591306379</v>
       </c>
       <c r="F47">
-        <v>-1.162129202145976</v>
+        <v>-1.057542847338122</v>
       </c>
       <c r="G47">
-        <v>-4.384769059249932</v>
+        <v>-3.404748263259483</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.906687809008005</v>
       </c>
       <c r="E48">
-        <v>-14.42693683914203</v>
+        <v>-11.38710809201315</v>
       </c>
       <c r="F48">
-        <v>-1.665731851208324</v>
+        <v>-1.237619151930498</v>
       </c>
       <c r="G48">
-        <v>-4.135349247775702</v>
+        <v>-4.034774874292643</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.299481772685099</v>
       </c>
       <c r="E49">
-        <v>-12.32817933249514</v>
+        <v>-11.69697798293601</v>
       </c>
       <c r="F49">
-        <v>-1.716988740991349</v>
+        <v>-1.333465402271415</v>
       </c>
       <c r="G49">
-        <v>-4.983345487660016</v>
+        <v>-3.395147681195596</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.8664238176014755</v>
       </c>
       <c r="E50">
-        <v>-12.48614609130471</v>
+        <v>-10.69198280336174</v>
       </c>
       <c r="F50">
-        <v>-1.547933036325818</v>
+        <v>-1.42428677594695</v>
       </c>
       <c r="G50">
-        <v>-4.602391080819463</v>
+        <v>-3.683204869658661</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.6345631060591369</v>
       </c>
       <c r="E51">
-        <v>-12.19339383213084</v>
+        <v>-10.04662091558063</v>
       </c>
       <c r="F51">
-        <v>-1.27364816374786</v>
+        <v>-1.471206334008917</v>
       </c>
       <c r="G51">
-        <v>-4.384593600336351</v>
+        <v>-3.347876401440343</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.6174084691287901</v>
       </c>
       <c r="E52">
-        <v>-12.32158587433998</v>
+        <v>-10.3264489099366</v>
       </c>
       <c r="F52">
-        <v>-1.622166352760293</v>
+        <v>-1.598318483601098</v>
       </c>
       <c r="G52">
-        <v>-4.350200342728862</v>
+        <v>-3.31304946236721</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.8115439333491525</v>
       </c>
       <c r="E53">
-        <v>-11.71782254879332</v>
+        <v>-9.681037208941399</v>
       </c>
       <c r="F53">
-        <v>-2.383299315311576</v>
+        <v>-1.847718371031556</v>
       </c>
       <c r="G53">
-        <v>-4.813600575679425</v>
+        <v>-2.79585286440349</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.200278694392136</v>
       </c>
       <c r="E54">
-        <v>-10.86507466535693</v>
+        <v>-8.807159465785221</v>
       </c>
       <c r="F54">
-        <v>-1.90592857679368</v>
+        <v>-1.56791574318355</v>
       </c>
       <c r="G54">
-        <v>-3.944181795610487</v>
+        <v>-3.652622049966873</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.753151026850778</v>
       </c>
       <c r="E55">
-        <v>-12.39949826964195</v>
+        <v>-8.004496504873664</v>
       </c>
       <c r="F55">
-        <v>-2.190954061116337</v>
+        <v>-1.851295261476845</v>
       </c>
       <c r="G55">
-        <v>-4.262275563751359</v>
+        <v>-3.932475706583624</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.424097939015635</v>
       </c>
       <c r="E56">
-        <v>-10.44185254154807</v>
+        <v>-7.943484374568322</v>
       </c>
       <c r="F56">
-        <v>-1.814620951452702</v>
+        <v>-2.243233156274417</v>
       </c>
       <c r="G56">
-        <v>-4.498853769078757</v>
+        <v>-3.503455489058392</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.158237696792076</v>
       </c>
       <c r="E57">
-        <v>-10.66930873400534</v>
+        <v>-7.339761805287733</v>
       </c>
       <c r="F57">
-        <v>-2.272837350515665</v>
+        <v>-2.07319666460397</v>
       </c>
       <c r="G57">
-        <v>-4.906213087140537</v>
+        <v>-3.467592349231468</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.896928305363336</v>
       </c>
       <c r="E58">
-        <v>-10.35447563557007</v>
+        <v>-7.517128546746157</v>
       </c>
       <c r="F58">
-        <v>-1.699192924077008</v>
+        <v>-2.307859895938626</v>
       </c>
       <c r="G58">
-        <v>-5.024647853807964</v>
+        <v>-3.551332598647332</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.589472863647842</v>
       </c>
       <c r="E59">
-        <v>-10.31421297316788</v>
+        <v>-7.860119696561118</v>
       </c>
       <c r="F59">
-        <v>-1.888030870688794</v>
+        <v>-2.329274850035798</v>
       </c>
       <c r="G59">
-        <v>-5.237966166176442</v>
+        <v>-3.581700232879067</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.193725694431567</v>
       </c>
       <c r="E60">
-        <v>-10.22745193965492</v>
+        <v>-7.161978444220602</v>
       </c>
       <c r="F60">
-        <v>-2.296632204161081</v>
+        <v>-2.563912401980967</v>
       </c>
       <c r="G60">
-        <v>-4.733968713277796</v>
+        <v>-3.868721220588339</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.681283587372625</v>
       </c>
       <c r="E61">
-        <v>-9.682173855917325</v>
+        <v>-6.632233026329316</v>
       </c>
       <c r="F61">
-        <v>-2.52395527193953</v>
+        <v>-2.427640994016032</v>
       </c>
       <c r="G61">
-        <v>-5.241961994642342</v>
+        <v>-4.435430337637399</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.037336554335941</v>
       </c>
       <c r="E62">
-        <v>-8.782393241437271</v>
+        <v>-6.5910737260736</v>
       </c>
       <c r="F62">
-        <v>-2.169362664762368</v>
+        <v>-2.235317277373265</v>
       </c>
       <c r="G62">
-        <v>-4.958592538662885</v>
+        <v>-3.658130797744221</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.259329484524974</v>
       </c>
       <c r="E63">
-        <v>-8.726557156922695</v>
+        <v>-6.270231342630155</v>
       </c>
       <c r="F63">
-        <v>-2.49668541703937</v>
+        <v>-2.29822681141147</v>
       </c>
       <c r="G63">
-        <v>-5.113092388435133</v>
+        <v>-3.986815001065221</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.353654598938817</v>
       </c>
       <c r="E64">
-        <v>-8.761960766714662</v>
+        <v>-6.067772326695229</v>
       </c>
       <c r="F64">
-        <v>-2.542296982972316</v>
+        <v>-2.484577999080053</v>
       </c>
       <c r="G64">
-        <v>-5.072750080493574</v>
+        <v>-4.509288608618539</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.334578635373221</v>
       </c>
       <c r="E65">
-        <v>-8.578530398559966</v>
+        <v>-6.632608889671952</v>
       </c>
       <c r="F65">
-        <v>-2.536412260942829</v>
+        <v>-2.672346523374825</v>
       </c>
       <c r="G65">
-        <v>-5.314866828508172</v>
+        <v>-4.341688930147396</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.224787188243775</v>
       </c>
       <c r="E66">
-        <v>-9.986215600792313</v>
+        <v>-6.441942020053</v>
       </c>
       <c r="F66">
-        <v>-2.54875162177493</v>
+        <v>-2.481030929861265</v>
       </c>
       <c r="G66">
-        <v>-5.353732633139216</v>
+        <v>-4.68916047940376</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.046918298559692</v>
       </c>
       <c r="E67">
-        <v>-8.093259123898012</v>
+        <v>-5.322290407078527</v>
       </c>
       <c r="F67">
-        <v>-2.517719322131255</v>
+        <v>-2.794983832257083</v>
       </c>
       <c r="G67">
-        <v>-5.462354942828243</v>
+        <v>-4.165349411452577</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.823806104369232</v>
       </c>
       <c r="E68">
-        <v>-8.56627634789521</v>
+        <v>-6.18920335721091</v>
       </c>
       <c r="F68">
-        <v>-2.560708276866938</v>
+        <v>-2.682715198155666</v>
       </c>
       <c r="G68">
-        <v>-5.63007049039326</v>
+        <v>-3.740152874025203</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.575563853918053</v>
       </c>
       <c r="E69">
-        <v>-8.372987491825818</v>
+        <v>-5.35758533349431</v>
       </c>
       <c r="F69">
-        <v>-2.87545227013243</v>
+        <v>-2.767803441036426</v>
       </c>
       <c r="G69">
-        <v>-5.417742031141024</v>
+        <v>-4.015106923243833</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.318971843988839</v>
       </c>
       <c r="E70">
-        <v>-8.919470149649452</v>
+        <v>-5.415146766605807</v>
       </c>
       <c r="F70">
-        <v>-2.590273537840255</v>
+        <v>-2.678772997685743</v>
       </c>
       <c r="G70">
-        <v>-5.538540527323491</v>
+        <v>-3.984630041009302</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.063997962077377</v>
       </c>
       <c r="E71">
-        <v>-8.108175917279278</v>
+        <v>-6.044849191268401</v>
       </c>
       <c r="F71">
-        <v>-2.559643824754341</v>
+        <v>-2.983074591471544</v>
       </c>
       <c r="G71">
-        <v>-5.244924932899989</v>
+        <v>-3.965094511782063</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.818598166084429</v>
       </c>
       <c r="E72">
-        <v>-7.876789009383352</v>
+        <v>-5.364224076389554</v>
       </c>
       <c r="F72">
-        <v>-2.309608579525935</v>
+        <v>-3.013344793104644</v>
       </c>
       <c r="G72">
-        <v>-5.233126148598028</v>
+        <v>-3.597428634736144</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.58784336571969</v>
       </c>
       <c r="E73">
-        <v>-8.642064888887582</v>
+        <v>-5.551603273878938</v>
       </c>
       <c r="F73">
-        <v>-2.779990382266412</v>
+        <v>-3.043576061469812</v>
       </c>
       <c r="G73">
-        <v>-4.73340923108166</v>
+        <v>-3.4927922218764</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.372172569506418</v>
       </c>
       <c r="E74">
-        <v>-8.907668946385463</v>
+        <v>-6.326044784774693</v>
       </c>
       <c r="F74">
-        <v>-3.114133083370663</v>
+        <v>-3.251077954034074</v>
       </c>
       <c r="G74">
-        <v>-5.286574906329561</v>
+        <v>-3.308229308062031</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.171955943775091</v>
       </c>
       <c r="E75">
-        <v>-8.778005150123839</v>
+        <v>-5.966461306195628</v>
       </c>
       <c r="F75">
-        <v>-2.983486290070736</v>
+        <v>-3.319694111110166</v>
       </c>
       <c r="G75">
-        <v>-4.72809580549113</v>
+        <v>-2.711983503711594</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.986253954736452</v>
       </c>
       <c r="E76">
-        <v>-8.586274089113083</v>
+        <v>-6.711186970653048</v>
       </c>
       <c r="F76">
-        <v>-3.446920575403933</v>
+        <v>-3.260883338981012</v>
       </c>
       <c r="G76">
-        <v>-4.456687350545059</v>
+        <v>-2.700833586335329</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.813510550149198</v>
       </c>
       <c r="E77">
-        <v>-9.004442435929379</v>
+        <v>-6.742754962960519</v>
       </c>
       <c r="F77">
-        <v>-3.255928873544868</v>
+        <v>-3.372224201591294</v>
       </c>
       <c r="G77">
-        <v>-4.600960925146498</v>
+        <v>-2.392548964627317</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.648776057678218</v>
       </c>
       <c r="E78">
-        <v>-10.06537332644639</v>
+        <v>-7.066703879573225</v>
       </c>
       <c r="F78">
-        <v>-3.209174988963461</v>
+        <v>-3.496922488571717</v>
       </c>
       <c r="G78">
-        <v>-4.693828348614133</v>
+        <v>-2.497619058952706</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.493525492196747</v>
       </c>
       <c r="E79">
-        <v>-11.14446792620817</v>
+        <v>-8.621107111180084</v>
       </c>
       <c r="F79">
-        <v>-3.683830339134981</v>
+        <v>-3.608437308336586</v>
       </c>
       <c r="G79">
-        <v>-3.518511850170998</v>
+        <v>-2.10368400305267</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.349773980278907</v>
       </c>
       <c r="E80">
-        <v>-11.54365743845832</v>
+        <v>-7.918690979376326</v>
       </c>
       <c r="F80">
-        <v>-3.286070678230534</v>
+        <v>-3.681601202454047</v>
       </c>
       <c r="G80">
-        <v>-3.983497834434872</v>
+        <v>-2.191360491114728</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.218664033595537</v>
       </c>
       <c r="E81">
-        <v>-11.57492655148128</v>
+        <v>-9.267759614053388</v>
       </c>
       <c r="F81">
-        <v>-3.338180786438442</v>
+        <v>-3.539402825722081</v>
       </c>
       <c r="G81">
-        <v>-3.832864701852493</v>
+        <v>-2.346260916897227</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.101207540318763</v>
       </c>
       <c r="E82">
-        <v>-12.64777185711247</v>
+        <v>-10.09176074448909</v>
       </c>
       <c r="F82">
-        <v>-3.405377121786135</v>
+        <v>-3.766001900390483</v>
       </c>
       <c r="G82">
-        <v>-3.117925908282566</v>
+        <v>-1.935600984932794</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.999313740275503</v>
       </c>
       <c r="E83">
-        <v>-13.78214553908588</v>
+        <v>-10.87017825556357</v>
       </c>
       <c r="F83">
-        <v>-3.564146160043703</v>
+        <v>-4.038427088149157</v>
       </c>
       <c r="G83">
-        <v>-3.577442871315564</v>
+        <v>-1.256406151550378</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.912514365767143</v>
       </c>
       <c r="E84">
-        <v>-14.01444267025735</v>
+        <v>-12.15755096036013</v>
       </c>
       <c r="F84">
-        <v>-3.668051596846456</v>
+        <v>-4.071961057349286</v>
       </c>
       <c r="G84">
-        <v>-3.276355375609928</v>
+        <v>-1.562019163008197</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.833696363160925</v>
       </c>
       <c r="E85">
-        <v>-15.85281292146319</v>
+        <v>-13.35586216684784</v>
       </c>
       <c r="F85">
-        <v>-3.757655270439876</v>
+        <v>-4.195625541811016</v>
       </c>
       <c r="G85">
-        <v>-2.901018964549518</v>
+        <v>-1.470168077021118</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.755194074828983</v>
       </c>
       <c r="E86">
-        <v>-16.47664191533784</v>
+        <v>-13.93938321358021</v>
       </c>
       <c r="F86">
-        <v>-4.186829936728091</v>
+        <v>-4.463292587208009</v>
       </c>
       <c r="G86">
-        <v>-3.195207283351313</v>
+        <v>-1.160423504730288</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.66957529193639</v>
       </c>
       <c r="E87">
-        <v>-17.66011331250241</v>
+        <v>-16.28230245329866</v>
       </c>
       <c r="F87">
-        <v>-4.162382329569269</v>
+        <v>-4.266397110869192</v>
       </c>
       <c r="G87">
-        <v>-3.495897513592236</v>
+        <v>-1.070270728604855</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.571907270692827</v>
       </c>
       <c r="E88">
-        <v>-18.25411777656254</v>
+        <v>-16.64456226001626</v>
       </c>
       <c r="F88">
-        <v>-3.907524329321765</v>
+        <v>-4.577343039592848</v>
       </c>
       <c r="G88">
-        <v>-2.740927603361442</v>
+        <v>-0.5584206616870585</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.459131408457337</v>
       </c>
       <c r="E89">
-        <v>-20.33112049407658</v>
+        <v>-17.75777438295183</v>
       </c>
       <c r="F89">
-        <v>-4.640234349548192</v>
+        <v>-4.575625833966845</v>
       </c>
       <c r="G89">
-        <v>-3.687468852313242</v>
+        <v>-0.8316168112243346</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.333601170796843</v>
       </c>
       <c r="E90">
-        <v>-21.56523381606893</v>
+        <v>-19.69929421510438</v>
       </c>
       <c r="F90">
-        <v>-4.491887829952648</v>
+        <v>-4.703712143624718</v>
       </c>
       <c r="G90">
-        <v>-3.290236493056092</v>
+        <v>-1.107074063364933</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.20269594030578</v>
       </c>
       <c r="E91">
-        <v>-24.297588235025</v>
+        <v>-22.10841521634097</v>
       </c>
       <c r="F91">
-        <v>-4.66613077129451</v>
+        <v>-4.645192128453947</v>
       </c>
       <c r="G91">
-        <v>-3.182239876473988</v>
+        <v>-1.498602352657918</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.077870857521487</v>
       </c>
       <c r="E92">
-        <v>-25.64487717941705</v>
+        <v>-24.16691458905967</v>
       </c>
       <c r="F92">
-        <v>-4.316235835658624</v>
+        <v>-4.882212065049567</v>
       </c>
       <c r="G92">
-        <v>-2.810012067674953</v>
+        <v>-1.913122380721142</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.974810067446648</v>
       </c>
       <c r="E93">
-        <v>-27.34660525591545</v>
+        <v>-26.79784477566595</v>
       </c>
       <c r="F93">
-        <v>-4.739870380756916</v>
+        <v>-4.798002719983177</v>
       </c>
       <c r="G93">
-        <v>-3.825369626751583</v>
+        <v>-1.605033081199948</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.910822161486565</v>
       </c>
       <c r="E94">
-        <v>-29.86194387923894</v>
+        <v>-27.72699707255976</v>
       </c>
       <c r="F94">
-        <v>-5.02301878454483</v>
+        <v>-4.721856703215638</v>
       </c>
       <c r="G94">
-        <v>-3.481483398314249</v>
+        <v>-1.888915671737991</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.903231987186177</v>
       </c>
       <c r="E95">
-        <v>-31.27175520001789</v>
+        <v>-30.51828505225166</v>
       </c>
       <c r="F95">
-        <v>-4.740569522844879</v>
+        <v>-4.870689474476626</v>
       </c>
       <c r="G95">
-        <v>-4.862401327473822</v>
+        <v>-2.672270199422497</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.969673411650264</v>
       </c>
       <c r="E96">
-        <v>-33.80194495384954</v>
+        <v>-32.72763695111387</v>
       </c>
       <c r="F96">
-        <v>-4.988269600364793</v>
+        <v>-5.020278545176369</v>
       </c>
       <c r="G96">
-        <v>-4.326241924661157</v>
+        <v>-2.551130717049486</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.113873732279628</v>
       </c>
       <c r="E97">
-        <v>-37.13589355930261</v>
+        <v>-34.70416641581973</v>
       </c>
       <c r="F97">
-        <v>-4.686896285347888</v>
+        <v>-5.110644316780364</v>
       </c>
       <c r="G97">
-        <v>-5.1415829433461</v>
+        <v>-3.026657478310399</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.349696536024747</v>
       </c>
       <c r="E98">
-        <v>-38.36209563720355</v>
+        <v>-36.8495513550866</v>
       </c>
       <c r="F98">
-        <v>-4.880584323103066</v>
+        <v>-5.047169836173449</v>
       </c>
       <c r="G98">
-        <v>-6.303538079992737</v>
+        <v>-3.694937443049838</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.652575319027972</v>
       </c>
       <c r="E99">
-        <v>-41.4147173234041</v>
+        <v>-40.3330052656659</v>
       </c>
       <c r="F99">
-        <v>-5.697255178175042</v>
+        <v>-5.340127766745314</v>
       </c>
       <c r="G99">
-        <v>-5.272634199063689</v>
+        <v>-4.284962732331985</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.035829115854533</v>
       </c>
       <c r="E100">
-        <v>-43.35939123770301</v>
+        <v>-42.25675989428636</v>
       </c>
       <c r="F100">
-        <v>-5.039933218542592</v>
+        <v>-5.225928208227971</v>
       </c>
       <c r="G100">
-        <v>-6.212375587477826</v>
+        <v>-5.025561564376802</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.434979126101039</v>
       </c>
       <c r="E101">
-        <v>-45.95329888505958</v>
+        <v>-45.49935559358269</v>
       </c>
       <c r="F101">
-        <v>-5.022884589025576</v>
+        <v>-5.063343709713109</v>
       </c>
       <c r="G101">
-        <v>-6.043587423158085</v>
+        <v>-4.992922895905128</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.909688106108757</v>
       </c>
       <c r="E102">
-        <v>-48.27502939489614</v>
+        <v>-47.9205925270268</v>
       </c>
       <c r="F102">
-        <v>-5.301823229672462</v>
+        <v>-5.212917869799602</v>
       </c>
       <c r="G102">
-        <v>-6.773582577840617</v>
+        <v>-5.634960166154764</v>
       </c>
     </row>
   </sheetData>
